--- a/i_test/test_D3_selezione_coorte/D3_PERSONS.xlsx
+++ b/i_test/test_D3_selezione_coorte/D3_PERSONS.xlsx
@@ -290,7 +290,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>20000101</v>
+        <v>19851231</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>7</v>
